--- a/3_N4_Armazenamento/Parametros/Pacote_DL_UL.xlsx
+++ b/3_N4_Armazenamento/Parametros/Pacote_DL_UL.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Temp\Pos-Doc\Frameworks\Artigo\Framework_DL_UL_MQTT_PAR\LoRa_Survey_MQTT_Net_GPS\LoRa_Survey_MQTT_Nodes\3_N4_Armazenamento\Parametros\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Temp\Pos-Doc\Frameworks\Artigo\Framework_DL_UL_MQTT_PAR\LoRa_Survey_MQTT_Net_GPS\LoRa_MQTT_Multiple_Nodes\3_N4_Armazenamento\Parametros\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="20 Bytes" sheetId="1" r:id="rId1"/>
     <sheet name="30 Bytes" sheetId="2" r:id="rId2"/>
+    <sheet name="DL20-UL30" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="49">
   <si>
     <t>UL_B</t>
   </si>
@@ -657,14 +658,14 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -959,17 +960,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="3"/>
       <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1"/>
+      <c r="G1" s="3"/>
       <c r="H1" t="s">
         <v>1</v>
       </c>
@@ -1106,7 +1107,7 @@
       <c r="H6">
         <v>26</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="L6" s="1" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1132,7 +1133,7 @@
       <c r="H7">
         <v>27</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="L7" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1158,7 +1159,7 @@
       <c r="H8">
         <v>28</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="L8" s="1" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1184,7 +1185,7 @@
       <c r="H9">
         <v>29</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="L9" s="1" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1213,7 +1214,7 @@
       <c r="I10" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="3"/>
+      <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -1237,7 +1238,7 @@
       <c r="H11">
         <v>31</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="L11" s="1" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1266,7 +1267,7 @@
       <c r="I12" t="s">
         <v>7</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="L12" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1289,7 +1290,7 @@
       <c r="H13">
         <v>33</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="L13" s="1" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1312,7 +1313,7 @@
       <c r="H14">
         <v>34</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="L14" s="1" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1335,7 +1336,7 @@
       <c r="H15">
         <v>35</v>
       </c>
-      <c r="L15" s="3"/>
+      <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -1356,7 +1357,7 @@
       <c r="H16">
         <v>36</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="L16" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1379,7 +1380,7 @@
       <c r="H17">
         <v>37</v>
       </c>
-      <c r="L17" s="2" t="s">
+      <c r="L17" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1402,7 +1403,7 @@
       <c r="H18">
         <v>38</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="L18" s="1" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1425,7 +1426,7 @@
       <c r="H19">
         <v>39</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="L19" s="1" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1530,17 +1531,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="3"/>
       <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1"/>
+      <c r="G1" s="3"/>
       <c r="H1" t="s">
         <v>1</v>
       </c>
@@ -2248,6 +2249,663 @@
       </c>
       <c r="H31">
         <v>61</v>
+      </c>
+      <c r="I31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.42578125" customWidth="1"/>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.140625" customWidth="1"/>
+    <col min="6" max="6" width="7.7109375" customWidth="1"/>
+    <col min="7" max="7" width="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="3"/>
+      <c r="H1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>25</v>
+      </c>
+      <c r="I5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>8</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+      <c r="H8">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>7</v>
+      </c>
+      <c r="H9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>8</v>
+      </c>
+      <c r="H10">
+        <v>30</v>
+      </c>
+      <c r="I10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" t="s">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>9</v>
+      </c>
+      <c r="H11">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>10</v>
+      </c>
+      <c r="H12">
+        <v>32</v>
+      </c>
+      <c r="I12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>11</v>
+      </c>
+      <c r="C13">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>11</v>
+      </c>
+      <c r="H13">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>14</v>
+      </c>
+      <c r="F14" t="s">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>12</v>
+      </c>
+      <c r="H14">
+        <v>34</v>
+      </c>
+      <c r="I14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15">
+        <v>13</v>
+      </c>
+      <c r="C15">
+        <v>15</v>
+      </c>
+      <c r="F15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>13</v>
+      </c>
+      <c r="H15">
+        <v>35</v>
+      </c>
+      <c r="I15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16">
+        <v>14</v>
+      </c>
+      <c r="C16">
+        <v>16</v>
+      </c>
+      <c r="F16" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>14</v>
+      </c>
+      <c r="H16">
+        <v>36</v>
+      </c>
+      <c r="I16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17">
+        <v>15</v>
+      </c>
+      <c r="C17">
+        <v>17</v>
+      </c>
+      <c r="F17" t="s">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>15</v>
+      </c>
+      <c r="H17">
+        <v>37</v>
+      </c>
+      <c r="I17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18">
+        <v>16</v>
+      </c>
+      <c r="C18">
+        <v>18</v>
+      </c>
+      <c r="D18" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>16</v>
+      </c>
+      <c r="H18">
+        <v>38</v>
+      </c>
+      <c r="I18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19">
+        <v>17</v>
+      </c>
+      <c r="C19">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>17</v>
+      </c>
+      <c r="H19">
+        <v>39</v>
+      </c>
+      <c r="I19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20">
+        <v>18</v>
+      </c>
+      <c r="C20">
+        <v>20</v>
+      </c>
+      <c r="F20" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>18</v>
+      </c>
+      <c r="H20">
+        <v>40</v>
+      </c>
+      <c r="I20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21">
+        <v>19</v>
+      </c>
+      <c r="C21">
+        <v>21</v>
+      </c>
+      <c r="F21" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>19</v>
+      </c>
+      <c r="H21">
+        <v>41</v>
+      </c>
+      <c r="I21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F22" t="s">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>20</v>
+      </c>
+      <c r="H22">
+        <v>42</v>
+      </c>
+      <c r="I22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F23" t="s">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>21</v>
+      </c>
+      <c r="H23">
+        <v>43</v>
+      </c>
+      <c r="I23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F24" t="s">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>22</v>
+      </c>
+      <c r="H24">
+        <v>44</v>
+      </c>
+      <c r="I24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F25" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>23</v>
+      </c>
+      <c r="H25">
+        <v>45</v>
+      </c>
+      <c r="I25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F26" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>24</v>
+      </c>
+      <c r="H26">
+        <v>46</v>
+      </c>
+      <c r="I26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F27" t="s">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>25</v>
+      </c>
+      <c r="H27">
+        <v>47</v>
+      </c>
+      <c r="I27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F28" t="s">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>26</v>
+      </c>
+      <c r="H28">
+        <v>48</v>
+      </c>
+      <c r="I28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F29" t="s">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>27</v>
+      </c>
+      <c r="H29">
+        <v>49</v>
+      </c>
+      <c r="I29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F30" t="s">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>28</v>
+      </c>
+      <c r="H30">
+        <v>50</v>
+      </c>
+      <c r="I30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F31" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>29</v>
+      </c>
+      <c r="H31">
+        <v>51</v>
       </c>
       <c r="I31" t="s">
         <v>31</v>

--- a/3_N4_Armazenamento/Parametros/Pacote_DL_UL.xlsx
+++ b/3_N4_Armazenamento/Parametros/Pacote_DL_UL.xlsx
@@ -9,12 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="20 Bytes" sheetId="1" r:id="rId1"/>
     <sheet name="30 Bytes" sheetId="2" r:id="rId2"/>
     <sheet name="DL20-UL30" sheetId="3" r:id="rId3"/>
+    <sheet name="ToA" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="68">
   <si>
     <t>UL_B</t>
   </si>
@@ -585,6 +586,63 @@
       </rPr>
       <t xml:space="preserve"> ;</t>
     </r>
+  </si>
+  <si>
+    <t>tMQTT_DL</t>
+  </si>
+  <si>
+    <t>ToA_LoRa_DL_N1</t>
+  </si>
+  <si>
+    <t>ToA_LoRa_UL_N1</t>
+  </si>
+  <si>
+    <t>tMQTT_UL</t>
+  </si>
+  <si>
+    <t>tTot_N1 [ms]</t>
+  </si>
+  <si>
+    <t>[ms]</t>
+  </si>
+  <si>
+    <t>LRC</t>
+  </si>
+  <si>
+    <t>[s]</t>
+  </si>
+  <si>
+    <t>MRC</t>
+  </si>
+  <si>
+    <t>SRC</t>
+  </si>
+  <si>
+    <t>tTot_N2 [ms]</t>
+  </si>
+  <si>
+    <t>ToA_LoRa_DL_N2</t>
+  </si>
+  <si>
+    <t>ToA_LoRa_UL_N2</t>
+  </si>
+  <si>
+    <t>ToA_LoRa_UL_N3</t>
+  </si>
+  <si>
+    <t>ToA_LoRa_DL_N3</t>
+  </si>
+  <si>
+    <t>tTot_N3 [ms]</t>
+  </si>
+  <si>
+    <t>tTot_N4 [ms]</t>
+  </si>
+  <si>
+    <t>ToA_LoRa_DL_N4</t>
+  </si>
+  <si>
+    <t>ToA_LoRa_UL_N4</t>
   </si>
 </sst>
 </file>
@@ -682,6 +740,66 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>154441</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6543675" cy="3583441"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2275,6 +2393,9 @@
     <col min="6" max="6" width="7.7109375" customWidth="1"/>
     <col min="7" max="7" width="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2918,4 +3039,261 @@
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="M4:Q22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="13" max="13" width="6.42578125" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" customWidth="1"/>
+    <col min="15" max="16" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="N4" t="s">
+        <v>54</v>
+      </c>
+      <c r="O4" t="s">
+        <v>54</v>
+      </c>
+      <c r="P4" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="N5" t="s">
+        <v>49</v>
+      </c>
+      <c r="O5" t="s">
+        <v>50</v>
+      </c>
+      <c r="P5" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="N6">
+        <v>125</v>
+      </c>
+      <c r="O6">
+        <v>2237</v>
+      </c>
+      <c r="P6">
+        <v>2237</v>
+      </c>
+      <c r="Q6">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="M7" t="s">
+        <v>55</v>
+      </c>
+      <c r="N7" t="s">
+        <v>53</v>
+      </c>
+      <c r="O7">
+        <f>SUM(N6:Q6)</f>
+        <v>4724</v>
+      </c>
+      <c r="P7">
+        <v>5</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="N9" t="s">
+        <v>54</v>
+      </c>
+      <c r="O9" t="s">
+        <v>54</v>
+      </c>
+      <c r="P9" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="N10" t="s">
+        <v>49</v>
+      </c>
+      <c r="O10" t="s">
+        <v>60</v>
+      </c>
+      <c r="P10" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="N11">
+        <v>125</v>
+      </c>
+      <c r="O11">
+        <v>1647</v>
+      </c>
+      <c r="P11">
+        <v>1647</v>
+      </c>
+      <c r="Q11">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="M12" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12" t="s">
+        <v>59</v>
+      </c>
+      <c r="O12">
+        <f>SUM(N11:Q11)</f>
+        <v>3544</v>
+      </c>
+      <c r="P12">
+        <v>4</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="N14" t="s">
+        <v>54</v>
+      </c>
+      <c r="O14" t="s">
+        <v>54</v>
+      </c>
+      <c r="P14" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="N15" t="s">
+        <v>49</v>
+      </c>
+      <c r="O15" t="s">
+        <v>63</v>
+      </c>
+      <c r="P15" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="N16">
+        <v>125</v>
+      </c>
+      <c r="O16">
+        <v>227</v>
+      </c>
+      <c r="P16">
+        <v>227</v>
+      </c>
+      <c r="Q16">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="M17" t="s">
+        <v>57</v>
+      </c>
+      <c r="N17" t="s">
+        <v>64</v>
+      </c>
+      <c r="O17">
+        <f>SUM(N16:Q16)</f>
+        <v>704</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="N19" t="s">
+        <v>54</v>
+      </c>
+      <c r="O19" t="s">
+        <v>54</v>
+      </c>
+      <c r="P19" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="N20" t="s">
+        <v>49</v>
+      </c>
+      <c r="O20" t="s">
+        <v>66</v>
+      </c>
+      <c r="P20" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="N21">
+        <v>125</v>
+      </c>
+      <c r="O21">
+        <v>60</v>
+      </c>
+      <c r="P21">
+        <v>60</v>
+      </c>
+      <c r="Q21">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="M22" t="s">
+        <v>58</v>
+      </c>
+      <c r="N22" t="s">
+        <v>65</v>
+      </c>
+      <c r="O22">
+        <f>SUM(N21:Q21)</f>
+        <v>370</v>
+      </c>
+      <c r="P22">
+        <v>0.5</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/3_N4_Armazenamento/Parametros/Pacote_DL_UL.xlsx
+++ b/3_N4_Armazenamento/Parametros/Pacote_DL_UL.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="70">
   <si>
     <t>UL_B</t>
   </si>
@@ -643,6 +643,12 @@
   </si>
   <si>
     <t>ToA_LoRa_UL_N4</t>
+  </si>
+  <si>
+    <t>sleep</t>
+  </si>
+  <si>
+    <t>tN2_N3_pkt</t>
   </si>
 </sst>
 </file>
@@ -3043,16 +3049,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="M4:Q22"/>
+  <dimension ref="M4:R24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="13" max="13" width="6.42578125" customWidth="1"/>
     <col min="14" max="14" width="13.42578125" customWidth="1"/>
-    <col min="15" max="16" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12" customWidth="1"/>
+    <col min="15" max="15" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.28515625" customWidth="1"/>
+    <col min="17" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="13:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="13:18" x14ac:dyDescent="0.25">
       <c r="N4" t="s">
         <v>54</v>
       </c>
@@ -3065,8 +3073,11 @@
       <c r="Q4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="5" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="R4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="13:18" x14ac:dyDescent="0.25">
       <c r="N5" t="s">
         <v>49</v>
       </c>
@@ -3074,13 +3085,16 @@
         <v>50</v>
       </c>
       <c r="P5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q5" t="s">
         <v>51</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="13:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="13:18" x14ac:dyDescent="0.25">
       <c r="N6">
         <v>125</v>
       </c>
@@ -3088,13 +3102,17 @@
         <v>2237</v>
       </c>
       <c r="P6">
+        <f>O6/2</f>
+        <v>1118.5</v>
+      </c>
+      <c r="Q6">
         <v>2237</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="13:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="13:18" x14ac:dyDescent="0.25">
       <c r="M7" t="s">
         <v>55</v>
       </c>
@@ -3102,45 +3120,64 @@
         <v>53</v>
       </c>
       <c r="O7">
-        <f>SUM(N6:Q6)</f>
-        <v>4724</v>
-      </c>
-      <c r="P7">
-        <v>5</v>
-      </c>
-      <c r="Q7" t="s">
+        <f>SUM(N6:R6)</f>
+        <v>5842.5</v>
+      </c>
+      <c r="Q7">
+        <v>6</v>
+      </c>
+      <c r="R7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="13:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="13:18" x14ac:dyDescent="0.25">
+      <c r="M8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N8">
+        <f>R6+N11+O11+P11+Q11+R11+N16+O16+P16+Q16+R16+N21+O21+P21+Q21+R21+N6</f>
+        <v>5835</v>
+      </c>
+      <c r="O8">
+        <v>6</v>
+      </c>
+      <c r="P8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="13:18" x14ac:dyDescent="0.25">
       <c r="N9" t="s">
         <v>54</v>
       </c>
       <c r="O9" t="s">
         <v>54</v>
       </c>
-      <c r="P9" t="s">
-        <v>54</v>
+      <c r="P9">
+        <f>Q12+Q17+Q22+((N6+O6)/1000)</f>
+        <v>9.3620000000000001</v>
       </c>
       <c r="Q9" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="10" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="R9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="13:18" x14ac:dyDescent="0.25">
       <c r="N10" t="s">
         <v>49</v>
       </c>
       <c r="O10" t="s">
         <v>60</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
         <v>61</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="13:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="13:18" x14ac:dyDescent="0.25">
       <c r="N11">
         <v>125</v>
       </c>
@@ -3148,13 +3185,17 @@
         <v>1647</v>
       </c>
       <c r="P11">
+        <f>O11/2</f>
+        <v>823.5</v>
+      </c>
+      <c r="Q11">
         <v>1647</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="13:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="13:18" x14ac:dyDescent="0.25">
       <c r="M12" t="s">
         <v>57</v>
       </c>
@@ -3162,45 +3203,64 @@
         <v>59</v>
       </c>
       <c r="O12">
-        <f>SUM(N11:Q11)</f>
-        <v>3544</v>
-      </c>
-      <c r="P12">
-        <v>4</v>
-      </c>
-      <c r="Q12" t="s">
+        <f>SUM(N11:R11)</f>
+        <v>4367.5</v>
+      </c>
+      <c r="Q12">
+        <v>5</v>
+      </c>
+      <c r="R12" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="13:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="13:18" x14ac:dyDescent="0.25">
+      <c r="M13" t="s">
+        <v>68</v>
+      </c>
+      <c r="N13">
+        <f>R11+N16+O16+P16+Q16+R16+N21+O21+P21+Q21+R21+N26+O26+P26+Q26+R26+N11+N6+O6+P6+Q6+R6</f>
+        <v>7310</v>
+      </c>
+      <c r="O13">
+        <v>8</v>
+      </c>
+      <c r="P13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="13:18" x14ac:dyDescent="0.25">
       <c r="N14" t="s">
         <v>54</v>
       </c>
       <c r="O14" t="s">
         <v>54</v>
       </c>
-      <c r="P14" t="s">
-        <v>54</v>
+      <c r="P14">
+        <f>Q7+Q12+Q22</f>
+        <v>12</v>
       </c>
       <c r="Q14" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="15" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="R14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="13:18" x14ac:dyDescent="0.25">
       <c r="N15" t="s">
         <v>49</v>
       </c>
       <c r="O15" t="s">
         <v>63</v>
       </c>
-      <c r="P15" t="s">
+      <c r="Q15" t="s">
         <v>62</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="R15" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="13:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="13:18" x14ac:dyDescent="0.25">
       <c r="N16">
         <v>125</v>
       </c>
@@ -3208,13 +3268,17 @@
         <v>227</v>
       </c>
       <c r="P16">
+        <f>O16/2</f>
+        <v>113.5</v>
+      </c>
+      <c r="Q16">
         <v>227</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="13:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="13:18" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
         <v>57</v>
       </c>
@@ -3222,45 +3286,64 @@
         <v>64</v>
       </c>
       <c r="O17">
-        <f>SUM(N16:Q16)</f>
-        <v>704</v>
-      </c>
-      <c r="P17">
+        <f>SUM(N16:R16)</f>
+        <v>817.5</v>
+      </c>
+      <c r="Q17">
         <v>1</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="13:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="13:18" x14ac:dyDescent="0.25">
+      <c r="M18" t="s">
+        <v>68</v>
+      </c>
+      <c r="N18">
+        <f>R16+N21+O21+P21+Q21+R21+N26+O26+P26+Q26+R26+N31+O31+P31+Q31+R31+N16+N11+O11+P11+Q11+R11+N6+O6+P6+Q6+R6</f>
+        <v>10860</v>
+      </c>
+      <c r="O18">
+        <v>11</v>
+      </c>
+      <c r="P18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="13:18" x14ac:dyDescent="0.25">
       <c r="N19" t="s">
         <v>54</v>
       </c>
       <c r="O19" t="s">
         <v>54</v>
       </c>
-      <c r="P19" t="s">
-        <v>54</v>
+      <c r="P19">
+        <f>Q22+Q12+Q7</f>
+        <v>12</v>
       </c>
       <c r="Q19" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="20" spans="13:17" x14ac:dyDescent="0.25">
+      <c r="R19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="13:18" x14ac:dyDescent="0.25">
       <c r="N20" t="s">
         <v>49</v>
       </c>
       <c r="O20" t="s">
         <v>66</v>
       </c>
-      <c r="P20" t="s">
+      <c r="Q20" t="s">
         <v>67</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="R20" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="13:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="13:18" x14ac:dyDescent="0.25">
       <c r="N21">
         <v>125</v>
       </c>
@@ -3268,13 +3351,17 @@
         <v>60</v>
       </c>
       <c r="P21">
+        <f>O21/2</f>
+        <v>30</v>
+      </c>
+      <c r="Q21">
         <v>60</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="13:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="13:18" x14ac:dyDescent="0.25">
       <c r="M22" t="s">
         <v>58</v>
       </c>
@@ -3282,14 +3369,35 @@
         <v>65</v>
       </c>
       <c r="O22">
-        <f>SUM(N21:Q21)</f>
-        <v>370</v>
-      </c>
-      <c r="P22">
-        <v>0.5</v>
-      </c>
-      <c r="Q22" t="s">
+        <f>SUM(N21:R21)</f>
+        <v>400</v>
+      </c>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+      <c r="R22" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="13:18" x14ac:dyDescent="0.25">
+      <c r="M23" t="s">
+        <v>68</v>
+      </c>
+      <c r="N23">
+        <f>R21+N26+O26+P26+Q26+R26+N31+O31+P31+Q31+R31+N36+O36+P36+Q36+R36+N21+N16+O16+P16+Q16+R16+N11+O11+P11+Q11+R11+N6+O6+P6+Q6+R6</f>
+        <v>11277.5</v>
+      </c>
+      <c r="O23">
+        <v>12</v>
+      </c>
+      <c r="P23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="13:18" x14ac:dyDescent="0.25">
+      <c r="O24">
+        <f>Q17+Q12+Q7</f>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
